--- a/subsystems database (For Thomas).xlsx
+++ b/subsystems database (For Thomas).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9ABD0E-BC26-4848-B9D1-98F1884C06C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D18481-5B1C-4C58-8313-3EFAFECE0937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DA27C19A-18DB-4E19-9AD3-8F88A97C8EE8}"/>
+    <workbookView xWindow="495" yWindow="495" windowWidth="23010" windowHeight="12210" activeTab="1" xr2:uid="{DA27C19A-18DB-4E19-9AD3-8F88A97C8EE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,13 @@
     <sheet name="Norm(mean)^2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">'Raw Data'!$B$2:$B$35</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'Raw Data'!$J$2:$J$35</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'Raw Data'!$K$2:$K$35</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'Raw Data'!$L$2:$L$35</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'Raw Data'!$N$2:$N$35</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'Raw Data'!$M$2:$M$35</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">'Raw Data'!$AB$2:$AB$35</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">'Raw Data'!$AB$2:$AB$35</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'Raw Data'!$N$2:$N$35</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'Raw Data'!$J$2:$J$35</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'Raw Data'!$B$2:$B$35</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'Raw Data'!$K$2:$K$35</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'Raw Data'!$L$2:$L$35</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">'Raw Data'!$M$2:$M$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -10595,7 +10595,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.0</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -10665,7 +10665,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.1</cx:f>
+        <cx:f>_xlchart.v1.2</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -10735,7 +10735,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.2</cx:f>
+        <cx:f>_xlchart.v1.4</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -10805,7 +10805,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.5</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -10875,7 +10875,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.5</cx:f>
+        <cx:f>_xlchart.v1.6</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -10945,7 +10945,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.4</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -11015,7 +11015,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.6</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
